--- a/inputs/odias_params_new.xlsx
+++ b/inputs/odias_params_new.xlsx
@@ -1,29 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hmdni\OneDrive\Documents\GitHub\odias\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DCFFB2-832C-4391-B986-E6920761F2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E1DAAA-3CD2-4F05-AC2C-A970A9C4D0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="30JUL24_HIGHAGGLOM_TANDEM" sheetId="13" r:id="rId1"/>
-    <sheet name="26JUL24_LOWAGGLOM_TANDEM" sheetId="12" r:id="rId2"/>
-    <sheet name="28AUG24_HIGHAGGLOM_TANDEM" sheetId="11" r:id="rId3"/>
-    <sheet name="20AUG24_HIGHAGGLOM_TANDEM" sheetId="10" r:id="rId4"/>
-    <sheet name="20AUG24_LOWAGGLOM_TANDEM" sheetId="9" r:id="rId5"/>
-    <sheet name="21AUG24_HIGHAGGLOM_TANDEM" sheetId="8" r:id="rId6"/>
-    <sheet name="19AUG24_LOWAGGLOM_TANDEM" sheetId="7" r:id="rId7"/>
-    <sheet name="ET017_NIT013_AIR16_DIST" sheetId="6" r:id="rId8"/>
-    <sheet name="23JUL24_SWEEP_ON_AIR" sheetId="5" r:id="rId9"/>
-    <sheet name="20JUL24_SWEEP_ON_NITROGEN" sheetId="4" r:id="rId10"/>
-    <sheet name="13SEP24_SWEEP_ON_FUEL" sheetId="3" r:id="rId11"/>
+    <sheet name="07FEB25_EXCOLAPS_TANDEM" sheetId="16" r:id="rId1"/>
+    <sheet name="06FEB25_R2_EXAGGLOM_TANDEM" sheetId="15" r:id="rId2"/>
+    <sheet name="06FEB25_R1_EXAGGLOM_TANDEM" sheetId="14" r:id="rId3"/>
+    <sheet name="30JUL24_HIGHAGGLOM_TANDEM" sheetId="13" r:id="rId4"/>
+    <sheet name="26JUL24_LOWAGGLOM_TANDEM" sheetId="12" r:id="rId5"/>
+    <sheet name="28AUG24_HIGHAGGLOM_TANDEM" sheetId="11" r:id="rId6"/>
+    <sheet name="20AUG24_HIGHAGGLOM_TANDEM" sheetId="10" r:id="rId7"/>
+    <sheet name="20AUG24_LOWAGGLOM_TANDEM" sheetId="9" r:id="rId8"/>
+    <sheet name="21AUG24_HIGHAGGLOM_TANDEM" sheetId="8" r:id="rId9"/>
+    <sheet name="19AUG24_LOWAGGLOM_TANDEM" sheetId="7" r:id="rId10"/>
+    <sheet name="ET017_NIT013_AIR16_DIST" sheetId="6" r:id="rId11"/>
+    <sheet name="23JUL24_SWEEP_ON_AIR" sheetId="5" r:id="rId12"/>
+    <sheet name="20JUL24_SWEEP_ON_NITROGEN" sheetId="4" r:id="rId13"/>
+    <sheet name="13SEP24_SWEEP_ON_FUEL" sheetId="3" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="269">
   <si>
     <t>fname</t>
   </si>
@@ -682,6 +685,177 @@
   </si>
   <si>
     <t>2024-07-30_193044_SMPS</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Experiments\PFA-RH122\PFA results\SMPS\FEB25-Final\FEB25-Final\TSI_Data\dndlogdp_MCC+_DLC+</t>
+  </si>
+  <si>
+    <t>D:\Hamed\CND\PhD\Experiments\PFA-RH122\PFA results\SMPS\FEB25-Final\FEB25-Final\TSI_Data\dndlogdp_MCC-_DLC+</t>
+  </si>
+  <si>
+    <t>2025-02-06_153534_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_154946_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_161211_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_162548_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_163937_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_165414_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_170904_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_173227_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_175756_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_181224_SMPS</t>
+  </si>
+  <si>
+    <t>#000000</t>
+  </si>
+  <si>
+    <t>#ffffff</t>
+  </si>
+  <si>
+    <t>#ffc5ff</t>
+  </si>
+  <si>
+    <t>#ff8aff</t>
+  </si>
+  <si>
+    <t>#d352ff</t>
+  </si>
+  <si>
+    <t>#991bff</t>
+  </si>
+  <si>
+    <t>#6000e2</t>
+  </si>
+  <si>
+    <t>#2900a7</t>
+  </si>
+  <si>
+    <t>#00006e</t>
+  </si>
+  <si>
+    <t>#000037</t>
+  </si>
+  <si>
+    <t>2025-02-06_202316_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_203727_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_210954_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_212615_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_220141_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_221534_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_223721_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_225352_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_231213_SMPS</t>
+  </si>
+  <si>
+    <t>06FEB25_R2_EXAGGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>06FEB25_R1_EXAGGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>2025-02-06_205441_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_155847_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_162120_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_164259_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_165639_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_171017_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_172822_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_174347_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_175850_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_181821_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_184135_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_185531_SMPS</t>
+  </si>
+  <si>
+    <t>#ecff81</t>
+  </si>
+  <si>
+    <t>#d8ff81</t>
+  </si>
+  <si>
+    <t>#c4ff81</t>
+  </si>
+  <si>
+    <t>#adff56</t>
+  </si>
+  <si>
+    <t>#95ff2b</t>
+  </si>
+  <si>
+    <t>#7eff00</t>
+  </si>
+  <si>
+    <t>#54d400</t>
+  </si>
+  <si>
+    <t>#2aa800</t>
+  </si>
+  <si>
+    <t>#007c00</t>
+  </si>
+  <si>
+    <t>#006700</t>
+  </si>
+  <si>
+    <t>#005300</t>
+  </si>
+  <si>
+    <t>07FEB25_EXCOLAPS_TANDEM</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C757B42-67CE-4B78-B430-7A91DEAA5F92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D03594-4B69-4DBE-A832-A85A927E2ABB}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1028,8 +1202,8 @@
     <col min="2" max="2" width="34.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
@@ -1087,40 +1261,40 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>186</v>
+        <v>268</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>212</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>200</v>
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>246</v>
       </c>
       <c r="H2" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I2" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K2" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L2" s="2">
         <v>1000</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>19</v>
@@ -1139,26 +1313,26 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>200</v>
+      <c r="G3" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="H3" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I3" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K3" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L3" s="2">
         <v>1000</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>129</v>
+        <v>257</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>19</v>
@@ -1178,25 +1352,25 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="5" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="H4" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I4" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K4" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L4" s="2">
         <v>1000</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>130</v>
+        <v>258</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>19</v>
@@ -1216,25 +1390,25 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="H5" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I5" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K5" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2">
         <v>1000</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>131</v>
+        <v>259</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>19</v>
@@ -1254,25 +1428,25 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5" t="s">
-        <v>203</v>
+        <v>250</v>
       </c>
       <c r="H6" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K6" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L6" s="2">
         <v>1000</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>132</v>
+        <v>260</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>19</v>
@@ -1292,25 +1466,25 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5" t="s">
-        <v>204</v>
+        <v>251</v>
       </c>
       <c r="H7" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I7" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K7" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2">
         <v>1000</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>133</v>
+        <v>261</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>19</v>
@@ -1330,25 +1504,25 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="H8" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I8" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K8" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2">
         <v>1000</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>134</v>
+        <v>262</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>19</v>
@@ -1368,25 +1542,25 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="H9" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I9" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K9" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L9" s="2">
         <v>1000</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>19</v>
@@ -1406,25 +1580,25 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="H10" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I10" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K10" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L10" s="2">
         <v>1000</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>136</v>
+        <v>264</v>
       </c>
       <c r="N10" s="6" t="s">
         <v>19</v>
@@ -1444,25 +1618,25 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5" t="s">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="H11" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I11" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K11" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L11" s="2">
         <v>1000</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>137</v>
+        <v>265</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>19</v>
@@ -1482,25 +1656,25 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="H12" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I12" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K12" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2">
         <v>1000</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>19</v>
@@ -1520,25 +1694,575 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" t="s">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="H13" s="2">
-        <v>1E-4</v>
+        <v>0.1</v>
       </c>
       <c r="I13" s="2">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
+        <v>0.01</v>
       </c>
       <c r="K13" s="1">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="L13" s="2">
         <v>1000</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>139</v>
+        <v>267</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F2A980-99F7-4378-B1A5-49E547FA6B9B}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>19</v>
@@ -1558,7 +2282,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>101</v>
       </c>
       <c r="H14" s="2">
         <v>1E-4</v>
@@ -1576,7 +2300,7 @@
         <v>1000</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="N14" s="6" t="s">
         <v>19</v>
@@ -1593,7 +2317,1306 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE5B189-3795-4D9F-8470-DCFD19DE4918}">
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.42578125" style="1" customWidth="1"/>
+    <col min="8" max="10" width="13.7109375" style="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="1"/>
+    <col min="13" max="13" width="10.7109375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G10" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G11" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>80</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>15</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15">
+        <v>19</v>
+      </c>
+      <c r="P15" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>87</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K16" s="1">
+        <v>15</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16">
+        <v>19</v>
+      </c>
+      <c r="P16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O17">
+        <v>19</v>
+      </c>
+      <c r="P17" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="L18" s="2"/>
+    </row>
+    <row r="19" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="7:17" x14ac:dyDescent="0.25">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="L20" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069A6CBD-9180-4207-8C39-A2C64C8EF28F}">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="13.7109375" style="1" customWidth="1"/>
+    <col min="11" max="14" width="9.140625" style="1"/>
+    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E3" s="2"/>
+      <c r="G3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E4" s="2"/>
+      <c r="G4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E5" s="2"/>
+      <c r="G5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E6" s="2"/>
+      <c r="G6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E7" s="2"/>
+      <c r="G7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E8" s="2"/>
+      <c r="G8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E9" s="2"/>
+      <c r="G9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E10" s="2"/>
+      <c r="G10" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E11" s="2"/>
+      <c r="G11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E12" s="2"/>
+      <c r="G12" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E13" s="2"/>
+      <c r="G13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E14" s="2"/>
+      <c r="G14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E15" s="2"/>
+      <c r="G15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>15</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O15">
+        <v>19</v>
+      </c>
+      <c r="P15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E16" s="2"/>
+      <c r="G16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K16" s="1">
+        <v>15</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O16">
+        <v>19</v>
+      </c>
+      <c r="P16" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="5:16" x14ac:dyDescent="0.25">
+      <c r="E17" s="2"/>
+      <c r="G17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O17">
+        <v>19</v>
+      </c>
+      <c r="P17" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5E4505-E9C8-42A1-8718-1B515BF5CEF0}">
   <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1919,7 +3942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20AA5E3-18D8-4B5E-AC08-AB63587E2B83}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2351,6 +4374,1596 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DFD7390-D362-40FA-9656-E468CEDCF082}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373A6E2E-7485-43B7-880B-A730001EE80C}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C757B42-67CE-4B78-B430-7A91DEAA5F92}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5155C0A2-4019-4528-8B1F-5147B306CFCF}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2902,7 +6515,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C47B65-DC64-4762-AC01-F458A5D6819D}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3476,7 +7089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3A47B7-5619-4AD8-9D1D-DCF8ECFDEA14}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3485,6 +7098,7 @@
     <col min="2" max="2" width="34.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4049,7 +7663,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AAC8C4-BFB5-4107-AD2D-75CC275963B2}">
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4654,7 +8268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13789820-1DD8-4FD1-AC5F-644F6AE28AED}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5226,1875 +8840,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F2A980-99F7-4378-B1A5-49E547FA6B9B}">
-  <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" t="s">
-        <v>101</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE5B189-3795-4D9F-8470-DCFD19DE4918}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.42578125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="13.7109375" style="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="1"/>
-    <col min="13" max="13" width="10.7109375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>16</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G3" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G6" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G7" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G8" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G10" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G11" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G13" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G14" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="G15" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K15" s="1">
-        <v>15</v>
-      </c>
-      <c r="L15" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O15">
-        <v>19</v>
-      </c>
-      <c r="P15" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K16" s="1">
-        <v>15</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O16">
-        <v>19</v>
-      </c>
-      <c r="P16" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="7:17" x14ac:dyDescent="0.25">
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K17" s="1">
-        <v>15</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O17">
-        <v>19</v>
-      </c>
-      <c r="P17" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="7:17" x14ac:dyDescent="0.25">
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="7:17" x14ac:dyDescent="0.25">
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="7:17" x14ac:dyDescent="0.25">
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069A6CBD-9180-4207-8C39-A2C64C8EF28F}">
-  <dimension ref="A1:P17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="27.28515625" style="1" customWidth="1"/>
-    <col min="8" max="10" width="13.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="9.140625" style="1"/>
-    <col min="15" max="15" width="10.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>16</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E3" s="2"/>
-      <c r="G3" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E4" s="2"/>
-      <c r="G4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E5" s="2"/>
-      <c r="G5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E6" s="2"/>
-      <c r="G6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E7" s="2"/>
-      <c r="G7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E8" s="2"/>
-      <c r="G8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E9" s="2"/>
-      <c r="G9" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E10" s="2"/>
-      <c r="G10" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E11" s="2"/>
-      <c r="G11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E12" s="2"/>
-      <c r="G12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E13" s="2"/>
-      <c r="G13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E14" s="2"/>
-      <c r="G14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E15" s="2"/>
-      <c r="G15" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K15" s="1">
-        <v>15</v>
-      </c>
-      <c r="L15" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O15">
-        <v>19</v>
-      </c>
-      <c r="P15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E16" s="2"/>
-      <c r="G16" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K16" s="1">
-        <v>15</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O16">
-        <v>19</v>
-      </c>
-      <c r="P16" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="5:16" x14ac:dyDescent="0.25">
-      <c r="E17" s="2"/>
-      <c r="G17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J17" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K17" s="1">
-        <v>15</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O17">
-        <v>19</v>
-      </c>
-      <c r="P17" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/inputs/odias_params_new.xlsx
+++ b/inputs/odias_params_new.xlsx
@@ -1,32 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hmdni\OneDrive\Documents\GitHub\odias\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E1DAAA-3CD2-4F05-AC2C-A970A9C4D0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292E227A-4F98-44D2-9714-2DD1E2046879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="07FEB25_EXCOLAPS_TANDEM" sheetId="16" r:id="rId1"/>
-    <sheet name="06FEB25_R2_EXAGGLOM_TANDEM" sheetId="15" r:id="rId2"/>
-    <sheet name="06FEB25_R1_EXAGGLOM_TANDEM" sheetId="14" r:id="rId3"/>
-    <sheet name="30JUL24_HIGHAGGLOM_TANDEM" sheetId="13" r:id="rId4"/>
-    <sheet name="26JUL24_LOWAGGLOM_TANDEM" sheetId="12" r:id="rId5"/>
-    <sheet name="28AUG24_HIGHAGGLOM_TANDEM" sheetId="11" r:id="rId6"/>
-    <sheet name="20AUG24_HIGHAGGLOM_TANDEM" sheetId="10" r:id="rId7"/>
-    <sheet name="20AUG24_LOWAGGLOM_TANDEM" sheetId="9" r:id="rId8"/>
-    <sheet name="21AUG24_HIGHAGGLOM_TANDEM" sheetId="8" r:id="rId9"/>
-    <sheet name="19AUG24_LOWAGGLOM_TANDEM" sheetId="7" r:id="rId10"/>
-    <sheet name="ET017_NIT013_AIR16_DIST" sheetId="6" r:id="rId11"/>
-    <sheet name="23JUL24_SWEEP_ON_AIR" sheetId="5" r:id="rId12"/>
-    <sheet name="20JUL24_SWEEP_ON_NITROGEN" sheetId="4" r:id="rId13"/>
-    <sheet name="13SEP24_SWEEP_ON_FUEL" sheetId="3" r:id="rId14"/>
+    <sheet name="MOBIL_DIST_FEB25" sheetId="21" r:id="rId1"/>
+    <sheet name="12FEB25_R2_EXAGLOM_TANDEM" sheetId="20" r:id="rId2"/>
+    <sheet name="12FEB25_R1_EXAGLOM_TANDEM" sheetId="19" r:id="rId3"/>
+    <sheet name="11FEB25_LOAGLOM_TANDEM" sheetId="18" r:id="rId4"/>
+    <sheet name="08FEB25_EXCOLAPS_TANDEM" sheetId="17" r:id="rId5"/>
+    <sheet name="07FEB25_EXCOLAPS_TANDEM" sheetId="16" r:id="rId6"/>
+    <sheet name="06FEB25_R2_EXAGGLOM_TANDEM" sheetId="15" r:id="rId7"/>
+    <sheet name="06FEB25_R1_EXAGGLOM_TANDEM" sheetId="14" r:id="rId8"/>
+    <sheet name="30JUL24_HIGHAGGLOM_TANDEM" sheetId="13" r:id="rId9"/>
+    <sheet name="26JUL24_LOWAGGLOM_TANDEM" sheetId="12" r:id="rId10"/>
+    <sheet name="28AUG24_HIGHAGGLOM_TANDEM" sheetId="11" r:id="rId11"/>
+    <sheet name="20AUG24_HIGHAGGLOM_TANDEM" sheetId="10" r:id="rId12"/>
+    <sheet name="20AUG24_LOWAGGLOM_TANDEM" sheetId="9" r:id="rId13"/>
+    <sheet name="21AUG24_HIGHAGGLOM_TANDEM" sheetId="8" r:id="rId14"/>
+    <sheet name="19AUG24_LOWAGGLOM_TANDEM" sheetId="7" r:id="rId15"/>
+    <sheet name="ET017_NIT013_AIR16_DIST" sheetId="6" r:id="rId16"/>
+    <sheet name="23JUL24_SWEEP_ON_AIR" sheetId="5" r:id="rId17"/>
+    <sheet name="20JUL24_SWEEP_ON_NITROGEN" sheetId="4" r:id="rId18"/>
+    <sheet name="13SEP24_SWEEP_ON_FUEL" sheetId="3" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="356">
   <si>
     <t>fname</t>
   </si>
@@ -856,13 +861,274 @@
   </si>
   <si>
     <t>07FEB25_EXCOLAPS_TANDEM</t>
+  </si>
+  <si>
+    <t>11FEB25_LOAGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>2025-02-11_094550_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_095236_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_095909_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_100630_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_101338_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_102046_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_102732_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_103515_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_104204_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_105004_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_105732_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_110429_SMPS</t>
+  </si>
+  <si>
+    <t>08FEB25_EXCOLAPS_TANDEM</t>
+  </si>
+  <si>
+    <t>12FEB25_R1_EXAGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>2025-02-12_174523_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_175203_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_180208_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_181029_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_181843_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_182534_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_183222_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_183916_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_184745_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_185502_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_190222_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_190951_SMPS</t>
+  </si>
+  <si>
+    <t>#ffd8ff</t>
+  </si>
+  <si>
+    <t>#ffafff</t>
+  </si>
+  <si>
+    <t>#fb85ff</t>
+  </si>
+  <si>
+    <t>#de60ff</t>
+  </si>
+  <si>
+    <t>#b839ff</t>
+  </si>
+  <si>
+    <t>#9017fa</t>
+  </si>
+  <si>
+    <t>#6904e7</t>
+  </si>
+  <si>
+    <t>#4200c2</t>
+  </si>
+  <si>
+    <t>#1f0099</t>
+  </si>
+  <si>
+    <t>#030073</t>
+  </si>
+  <si>
+    <t>#00004c</t>
+  </si>
+  <si>
+    <t>#000025</t>
+  </si>
+  <si>
+    <t>12FEB25_R2_EXAGLOM_TANDEM</t>
+  </si>
+  <si>
+    <t>2025-02-12_194454_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_195204_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_195928_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_200709_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_201403_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_202753_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_203508_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_204158_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_204900_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_205549_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_210424_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_211126_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_211822_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_163703_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_162632_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_150142_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_151743_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_152724_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_153729_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_155616_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_161642_SMPS</t>
+  </si>
+  <si>
+    <t>MOBIL_DIST_FEB25</t>
+  </si>
+  <si>
+    <t>2025-02-06_131033_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_141208_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_131248_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-11_093550_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_171450_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_135422_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_135008_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-06_194637_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_173633_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-12_193113_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_144325_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-07_203409_SMPS</t>
+  </si>
+  <si>
+    <t>2025-02-08_144418_SMPS</t>
+  </si>
+  <si>
+    <t>#80d4ff</t>
+  </si>
+  <si>
+    <t>#80a8ff</t>
+  </si>
+  <si>
+    <t>#807cff</t>
+  </si>
+  <si>
+    <t>#aa52ed</t>
+  </si>
+  <si>
+    <t>#d529db</t>
+  </si>
+  <si>
+    <t>#ff00c8</t>
+  </si>
+  <si>
+    <t>#eb0085</t>
+  </si>
+  <si>
+    <t>#d60043</t>
+  </si>
+  <si>
+    <t>#c20000</t>
+  </si>
+  <si>
+    <t>#810000</t>
+  </si>
+  <si>
+    <t>#410000</t>
+  </si>
+  <si>
+    <t>#80ffff</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,13 +1142,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -897,7 +1183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -915,6 +1201,42 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1194,7 +1516,581 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D03594-4B69-4DBE-A832-A85A927E2ABB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F52B2F-3150-4970-93DA-CF1EF1834400}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="12">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="13">
+        <v>1</v>
+      </c>
+      <c r="J2" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="10">
+        <v>20</v>
+      </c>
+      <c r="L2" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="8">
+        <v>19</v>
+      </c>
+      <c r="P2" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="13">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="10">
+        <v>20</v>
+      </c>
+      <c r="L3" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="8">
+        <v>19</v>
+      </c>
+      <c r="P3" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="13">
+        <v>1</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="10">
+        <v>20</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="8">
+        <v>19</v>
+      </c>
+      <c r="P4" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="13">
+        <v>1</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="10">
+        <v>20</v>
+      </c>
+      <c r="L5" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="8">
+        <v>19</v>
+      </c>
+      <c r="P5" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="13">
+        <v>1</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="10">
+        <v>20</v>
+      </c>
+      <c r="L6" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="8">
+        <v>19</v>
+      </c>
+      <c r="P6" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="H7" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="16">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="15">
+        <v>20</v>
+      </c>
+      <c r="L7" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="18">
+        <v>19</v>
+      </c>
+      <c r="P7" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="10">
+        <v>20</v>
+      </c>
+      <c r="L8" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="13">
+        <v>1</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="10">
+        <v>20</v>
+      </c>
+      <c r="L9" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="8">
+        <v>19</v>
+      </c>
+      <c r="P9" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="13">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="10">
+        <v>20</v>
+      </c>
+      <c r="L10" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10" s="8">
+        <v>19</v>
+      </c>
+      <c r="P10" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="13">
+        <v>1</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="10">
+        <v>20</v>
+      </c>
+      <c r="L11" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11" s="8">
+        <v>19</v>
+      </c>
+      <c r="P11" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="16">
+        <v>1</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="15">
+        <v>20</v>
+      </c>
+      <c r="L12" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="18">
+        <v>19</v>
+      </c>
+      <c r="P12" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="16">
+        <v>1</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="15">
+        <v>20</v>
+      </c>
+      <c r="L13" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="18">
+        <v>19</v>
+      </c>
+      <c r="P13" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="16">
+        <v>1</v>
+      </c>
+      <c r="J14" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K14" s="15">
+        <v>20</v>
+      </c>
+      <c r="L14" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="18">
+        <v>19</v>
+      </c>
+      <c r="P14" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5155C0A2-4019-4528-8B1F-5147B306CFCF}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1261,34 +2157,34 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>268</v>
+        <v>187</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>212</v>
+        <v>33</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>213</v>
+        <v>34</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="H2" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I2" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J2" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L2" s="2">
         <v>1000</v>
@@ -1314,25 +2210,25 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="5" t="s">
-        <v>247</v>
+        <v>189</v>
       </c>
       <c r="H3" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I3" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J3" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K3" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L3" s="2">
         <v>1000</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>19</v>
@@ -1352,25 +2248,25 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="5" t="s">
-        <v>248</v>
+        <v>190</v>
       </c>
       <c r="H4" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J4" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K4" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L4" s="2">
         <v>1000</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>258</v>
+        <v>106</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>19</v>
@@ -1390,25 +2286,25 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J5" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K5" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L5" s="2">
         <v>1000</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>259</v>
+        <v>107</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>19</v>
@@ -1428,25 +2324,25 @@
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="H6" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I6" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J6" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K6" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L6" s="2">
         <v>1000</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>260</v>
+        <v>108</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>19</v>
@@ -1466,25 +2362,25 @@
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="H7" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I7" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J7" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K7" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L7" s="2">
         <v>1000</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>261</v>
+        <v>109</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>19</v>
@@ -1504,25 +2400,25 @@
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5" t="s">
-        <v>252</v>
+        <v>194</v>
       </c>
       <c r="H8" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I8" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J8" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K8" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L8" s="2">
         <v>1000</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>262</v>
+        <v>110</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>19</v>
@@ -1542,25 +2438,25 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="H9" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I9" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J9" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K9" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L9" s="2">
         <v>1000</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>263</v>
+        <v>111</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>19</v>
@@ -1580,25 +2476,25 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5" t="s">
-        <v>254</v>
+        <v>196</v>
       </c>
       <c r="H10" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I10" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J10" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K10" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L10" s="2">
         <v>1000</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>264</v>
+        <v>112</v>
       </c>
       <c r="N10" s="6" t="s">
         <v>19</v>
@@ -1618,25 +2514,25 @@
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="H11" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I11" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J11" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K11" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L11" s="2">
         <v>1000</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>265</v>
+        <v>113</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>19</v>
@@ -1656,25 +2552,25 @@
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" t="s">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="H12" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I12" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J12" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K12" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L12" s="2">
         <v>1000</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>266</v>
+        <v>114</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>19</v>
@@ -1694,25 +2590,25 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" t="s">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="H13" s="2">
-        <v>0.1</v>
+        <v>1E-4</v>
       </c>
       <c r="I13" s="2">
-        <v>1</v>
+        <v>1E-3</v>
       </c>
       <c r="J13" s="2">
-        <v>0.01</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="K13" s="1">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="L13" s="2">
         <v>1000</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>267</v>
+        <v>115</v>
       </c>
       <c r="N13" s="6" t="s">
         <v>19</v>
@@ -1745,7 +2641,2334 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C47B65-DC64-4762-AC01-F458A5D6819D}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>185</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3A47B7-5619-4AD8-9D1D-DCF8ECFDEA14}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>173</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AAC8C4-BFB5-4107-AD2D-75CC275963B2}">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>163</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>163</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J15" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>15</v>
+      </c>
+      <c r="L15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O15">
+        <v>19</v>
+      </c>
+      <c r="P15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13789820-1DD8-4FD1-AC5F-644F6AE28AED}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>126</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>126</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F2A980-99F7-4378-B1A5-49E547FA6B9B}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2317,7 +5540,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE5B189-3795-4D9F-8470-DCFD19DE4918}">
   <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2998,7 +6221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069A6CBD-9180-4207-8C39-A2C64C8EF28F}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3616,7 +6839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5E4505-E9C8-42A1-8718-1B515BF5CEF0}">
   <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3942,7 +7165,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20AA5E3-18D8-4B5E-AC08-AB63587E2B83}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4374,6 +7597,2744 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B95137-FEB9-4E2C-B66C-6707D12DE928}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" t="s">
+        <v>225</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>319</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>320</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>321</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K14" s="1">
+        <v>50</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766A1B92-ECA3-413F-8793-59F03099027E}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>294</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>295</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7D1D9CF-0A91-45D6-BABB-CA45EEB326F8}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>280</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465DD4B3-EF50-4C4C-8052-3ED0AB0386FC}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>10</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="6"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="6"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D03594-4B69-4DBE-A832-A85A927E2ABB}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>256</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DFD7390-D362-40FA-9656-E468CEDCF082}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4881,7 +10842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373A6E2E-7485-43B7-880B-A730001EE80C}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4982,7 +10943,7 @@
         <v>1000</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="N2" s="6" t="s">
         <v>19</v>
@@ -5020,7 +10981,7 @@
         <v>1000</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>105</v>
+        <v>226</v>
       </c>
       <c r="N3" s="6" t="s">
         <v>19</v>
@@ -5058,7 +11019,7 @@
         <v>1000</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="N4" s="6" t="s">
         <v>19</v>
@@ -5096,7 +11057,7 @@
         <v>1000</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>107</v>
+        <v>228</v>
       </c>
       <c r="N5" s="6" t="s">
         <v>19</v>
@@ -5134,7 +11095,7 @@
         <v>1000</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>108</v>
+        <v>229</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>19</v>
@@ -5172,7 +11133,7 @@
         <v>1000</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>109</v>
+        <v>230</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>19</v>
@@ -5210,7 +11171,7 @@
         <v>1000</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>110</v>
+        <v>231</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>19</v>
@@ -5248,7 +11209,7 @@
         <v>1000</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>111</v>
+        <v>232</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>19</v>
@@ -5286,7 +11247,7 @@
         <v>1000</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>112</v>
+        <v>233</v>
       </c>
       <c r="N10" s="6" t="s">
         <v>19</v>
@@ -5324,7 +11285,7 @@
         <v>1000</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>113</v>
+        <v>224</v>
       </c>
       <c r="N11" s="6" t="s">
         <v>19</v>
@@ -5389,7 +11350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C757B42-67CE-4B78-B430-7A91DEAA5F92}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5961,2883 +11922,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5155C0A2-4019-4528-8B1F-5147B306CFCF}">
-  <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" customWidth="1"/>
-    <col min="7" max="7" width="27.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>12</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>198</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>199</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="6"/>
-      <c r="P14" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C47B65-DC64-4762-AC01-F458A5D6819D}">
-  <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="20.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>185</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3A47B7-5619-4AD8-9D1D-DCF8ECFDEA14}">
-  <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>173</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" t="s">
-        <v>173</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AAC8C4-BFB5-4107-AD2D-75CC275963B2}">
-  <dimension ref="A1:P15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>14</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>162</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>163</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="G15" t="s">
-        <v>164</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I15" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K15" s="1">
-        <v>15</v>
-      </c>
-      <c r="L15" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M15" t="s">
-        <v>142</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O15">
-        <v>19</v>
-      </c>
-      <c r="P15" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13789820-1DD8-4FD1-AC5F-644F6AE28AED}">
-  <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>126</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>126</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/inputs/odias_params_new.xlsx
+++ b/inputs/odias_params_new.xlsx
@@ -1,37 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hmdni\OneDrive\Documents\GitHub\odias\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292E227A-4F98-44D2-9714-2DD1E2046879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9240CD-D008-4D08-9B12-F3C309C84801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MOBIL_DIST_FEB25" sheetId="21" r:id="rId1"/>
-    <sheet name="12FEB25_R2_EXAGLOM_TANDEM" sheetId="20" r:id="rId2"/>
-    <sheet name="12FEB25_R1_EXAGLOM_TANDEM" sheetId="19" r:id="rId3"/>
-    <sheet name="11FEB25_LOAGLOM_TANDEM" sheetId="18" r:id="rId4"/>
-    <sheet name="08FEB25_EXCOLAPS_TANDEM" sheetId="17" r:id="rId5"/>
-    <sheet name="07FEB25_EXCOLAPS_TANDEM" sheetId="16" r:id="rId6"/>
-    <sheet name="06FEB25_R2_EXAGGLOM_TANDEM" sheetId="15" r:id="rId7"/>
-    <sheet name="06FEB25_R1_EXAGGLOM_TANDEM" sheetId="14" r:id="rId8"/>
-    <sheet name="30JUL24_HIGHAGGLOM_TANDEM" sheetId="13" r:id="rId9"/>
-    <sheet name="26JUL24_LOWAGGLOM_TANDEM" sheetId="12" r:id="rId10"/>
-    <sheet name="28AUG24_HIGHAGGLOM_TANDEM" sheetId="11" r:id="rId11"/>
-    <sheet name="20AUG24_HIGHAGGLOM_TANDEM" sheetId="10" r:id="rId12"/>
-    <sheet name="20AUG24_LOWAGGLOM_TANDEM" sheetId="9" r:id="rId13"/>
-    <sheet name="21AUG24_HIGHAGGLOM_TANDEM" sheetId="8" r:id="rId14"/>
-    <sheet name="19AUG24_LOWAGGLOM_TANDEM" sheetId="7" r:id="rId15"/>
-    <sheet name="ET017_NIT013_AIR16_DIST" sheetId="6" r:id="rId16"/>
-    <sheet name="23JUL24_SWEEP_ON_AIR" sheetId="5" r:id="rId17"/>
-    <sheet name="20JUL24_SWEEP_ON_NITROGEN" sheetId="4" r:id="rId18"/>
-    <sheet name="13SEP24_SWEEP_ON_FUEL" sheetId="3" r:id="rId19"/>
+    <sheet name="MAY25_TANDEM_COMPARE" sheetId="22" r:id="rId1"/>
+    <sheet name="MOBIL_DIST_FEB25" sheetId="21" r:id="rId2"/>
+    <sheet name="12FEB25_R2_EXAGLOM_TANDEM" sheetId="20" r:id="rId3"/>
+    <sheet name="12FEB25_R1_EXAGLOM_TANDEM" sheetId="19" r:id="rId4"/>
+    <sheet name="11FEB25_LOAGLOM_TANDEM" sheetId="18" r:id="rId5"/>
+    <sheet name="08FEB25_EXCOLAPS_TANDEM" sheetId="17" r:id="rId6"/>
+    <sheet name="07FEB25_EXCOLAPS_TANDEM" sheetId="16" r:id="rId7"/>
+    <sheet name="06FEB25_R2_EXAGGLOM_TANDEM" sheetId="15" r:id="rId8"/>
+    <sheet name="06FEB25_R1_EXAGGLOM_TANDEM" sheetId="14" r:id="rId9"/>
+    <sheet name="30JUL24_HIGHAGGLOM_TANDEM" sheetId="13" r:id="rId10"/>
+    <sheet name="26JUL24_LOWAGGLOM_TANDEM" sheetId="12" r:id="rId11"/>
+    <sheet name="28AUG24_HIGHAGGLOM_TANDEM" sheetId="11" r:id="rId12"/>
+    <sheet name="20AUG24_HIGHAGGLOM_TANDEM" sheetId="10" r:id="rId13"/>
+    <sheet name="20AUG24_LOWAGGLOM_TANDEM" sheetId="9" r:id="rId14"/>
+    <sheet name="21AUG24_HIGHAGGLOM_TANDEM" sheetId="8" r:id="rId15"/>
+    <sheet name="19AUG24_LOWAGGLOM_TANDEM" sheetId="7" r:id="rId16"/>
+    <sheet name="ET017_NIT013_AIR16_DIST" sheetId="6" r:id="rId17"/>
+    <sheet name="23JUL24_SWEEP_ON_AIR" sheetId="5" r:id="rId18"/>
+    <sheet name="20JUL24_SWEEP_ON_NITROGEN" sheetId="4" r:id="rId19"/>
+    <sheet name="13SEP24_SWEEP_ON_FUEL" sheetId="3" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="367">
   <si>
     <t>fname</t>
   </si>
@@ -1122,6 +1123,39 @@
   </si>
   <si>
     <t>#80ffff</t>
+  </si>
+  <si>
+    <t>#ffff80</t>
+  </si>
+  <si>
+    <t>#ffea68</t>
+  </si>
+  <si>
+    <t>#ffd451</t>
+  </si>
+  <si>
+    <t>#ffbe39</t>
+  </si>
+  <si>
+    <t>#ffa622</t>
+  </si>
+  <si>
+    <t>#ff8e0b</t>
+  </si>
+  <si>
+    <t>#f46a00</t>
+  </si>
+  <si>
+    <t>#de3b00</t>
+  </si>
+  <si>
+    <t>#c80c00</t>
+  </si>
+  <si>
+    <t>#8e0000</t>
+  </si>
+  <si>
+    <t>MAY25_TANDEM_COMPARE</t>
   </si>
 </sst>
 </file>
@@ -1516,573 +1550,555 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F52B2F-3150-4970-93DA-CF1EF1834400}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53FACEA6-899F-407E-B4C6-0054987F7E64}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.85546875" customWidth="1"/>
     <col min="7" max="7" width="27.7109375" customWidth="1"/>
-    <col min="14" max="14" width="5.42578125" customWidth="1"/>
-    <col min="15" max="15" width="6.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="19" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="J1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="19" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="12">
-        <v>13</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="B2" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" t="s">
+        <v>356</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="1">
+        <v>50</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="1">
+        <v>50</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="1">
+        <v>50</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="1">
+        <v>50</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="1">
+        <v>50</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F8" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="H2" s="13">
+      <c r="G8" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="H8" s="2">
         <v>0.1</v>
       </c>
-      <c r="I2" s="13">
-        <v>1</v>
-      </c>
-      <c r="J2" s="13">
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2">
         <v>0.01</v>
       </c>
-      <c r="K2" s="10">
-        <v>20</v>
-      </c>
-      <c r="L2" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="N2" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="8">
-        <v>19</v>
-      </c>
-      <c r="P2" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="H3" s="13">
+      <c r="K8" s="1">
+        <v>50</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="H9" s="2">
         <v>0.1</v>
       </c>
-      <c r="I3" s="13">
-        <v>1</v>
-      </c>
-      <c r="J3" s="13">
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2">
         <v>0.01</v>
       </c>
-      <c r="K3" s="10">
-        <v>20</v>
-      </c>
-      <c r="L3" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="N3" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" s="8">
-        <v>19</v>
-      </c>
-      <c r="P3" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H10" s="2">
         <v>0.1</v>
       </c>
-      <c r="I4" s="13">
-        <v>1</v>
-      </c>
-      <c r="J4" s="13">
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2">
         <v>0.01</v>
       </c>
-      <c r="K4" s="10">
-        <v>20</v>
-      </c>
-      <c r="L4" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>345</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" s="8">
-        <v>19</v>
-      </c>
-      <c r="P4" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="H5" s="13">
+      <c r="K10" s="1">
+        <v>50</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="H11" s="2">
         <v>0.1</v>
       </c>
-      <c r="I5" s="13">
-        <v>1</v>
-      </c>
-      <c r="J5" s="13">
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2">
         <v>0.01</v>
       </c>
-      <c r="K5" s="10">
-        <v>20</v>
-      </c>
-      <c r="L5" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="N5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5" s="8">
-        <v>19</v>
-      </c>
-      <c r="P5" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H6" s="13">
+      <c r="K11" s="1">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>326</v>
+      </c>
+      <c r="H12" s="2">
         <v>0.1</v>
       </c>
-      <c r="I6" s="13">
-        <v>1</v>
-      </c>
-      <c r="J6" s="13">
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
         <v>0.01</v>
       </c>
-      <c r="K6" s="10">
-        <v>20</v>
-      </c>
-      <c r="L6" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>347</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="8">
-        <v>19</v>
-      </c>
-      <c r="P6" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="H7" s="16">
+      <c r="K12" s="1">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H13" s="2">
         <v>0.1</v>
       </c>
-      <c r="I7" s="16">
-        <v>1</v>
-      </c>
-      <c r="J7" s="16">
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
         <v>0.01</v>
       </c>
-      <c r="K7" s="15">
-        <v>20</v>
-      </c>
-      <c r="L7" s="16">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" s="18">
-        <v>19</v>
-      </c>
-      <c r="P7" s="15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="I8" s="13">
-        <v>1</v>
-      </c>
-      <c r="J8" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="K8" s="10">
-        <v>20</v>
-      </c>
-      <c r="L8" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>349</v>
-      </c>
-      <c r="N8" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8" s="8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="H9" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="I9" s="13">
-        <v>1</v>
-      </c>
-      <c r="J9" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="K9" s="10">
-        <v>20</v>
-      </c>
-      <c r="L9" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="N9" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9" s="8">
-        <v>19</v>
-      </c>
-      <c r="P9" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="I10" s="13">
-        <v>1</v>
-      </c>
-      <c r="J10" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="K10" s="10">
-        <v>20</v>
-      </c>
-      <c r="L10" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>351</v>
-      </c>
-      <c r="N10" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10" s="8">
-        <v>19</v>
-      </c>
-      <c r="P10" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0.1</v>
-      </c>
-      <c r="I11" s="13">
-        <v>1</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0.01</v>
-      </c>
-      <c r="K11" s="10">
-        <v>20</v>
-      </c>
-      <c r="L11" s="13">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="N11" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11" s="8">
-        <v>19</v>
-      </c>
-      <c r="P11" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="H12" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="I12" s="16">
-        <v>1</v>
-      </c>
-      <c r="J12" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="K12" s="15">
-        <v>20</v>
-      </c>
-      <c r="L12" s="16">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>353</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" s="18">
-        <v>19</v>
-      </c>
-      <c r="P12" s="15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="H13" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="I13" s="16">
-        <v>1</v>
-      </c>
-      <c r="J13" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="K13" s="15">
-        <v>20</v>
-      </c>
-      <c r="L13" s="16">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>354</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13" s="18">
-        <v>19</v>
-      </c>
-      <c r="P13" s="15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="H14" s="16">
-        <v>0.1</v>
-      </c>
-      <c r="I14" s="16">
-        <v>1</v>
-      </c>
-      <c r="J14" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="K14" s="15">
-        <v>20</v>
-      </c>
-      <c r="L14" s="16">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="15" t="s">
+      <c r="K13" s="1">
+        <v>50</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="N14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14" s="18">
-        <v>19</v>
-      </c>
-      <c r="P14" s="15" t="b">
-        <v>1</v>
-      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="6"/>
+      <c r="P14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2090,6 +2106,580 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C757B42-67CE-4B78-B430-7A91DEAA5F92}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>13</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I2" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15</v>
+      </c>
+      <c r="L2" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <v>19</v>
+      </c>
+      <c r="P3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K4" s="1">
+        <v>15</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4">
+        <v>19</v>
+      </c>
+      <c r="P4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>15</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>19</v>
+      </c>
+      <c r="P5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K6" s="1">
+        <v>15</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6">
+        <v>19</v>
+      </c>
+      <c r="P6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K7" s="1">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7">
+        <v>19</v>
+      </c>
+      <c r="P7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K8" s="1">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J9" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9">
+        <v>19</v>
+      </c>
+      <c r="P9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J10" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K10" s="1">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10">
+        <v>19</v>
+      </c>
+      <c r="P10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K11" s="1">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11">
+        <v>19</v>
+      </c>
+      <c r="P11" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" t="s">
+        <v>209</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <v>19</v>
+      </c>
+      <c r="P12" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" t="s">
+        <v>210</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J13" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13">
+        <v>19</v>
+      </c>
+      <c r="P13" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1E-4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1E-3</v>
+      </c>
+      <c r="J14" s="2">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14">
+        <v>19</v>
+      </c>
+      <c r="P14" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5155C0A2-4019-4528-8B1F-5147B306CFCF}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2641,7 +3231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16C47B65-DC64-4762-AC01-F458A5D6819D}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3215,7 +3805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3A47B7-5619-4AD8-9D1D-DCF8ECFDEA14}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3789,7 +4379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5AAC8C4-BFB5-4107-AD2D-75CC275963B2}">
   <dimension ref="A1:P15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4394,7 +4984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13789820-1DD8-4FD1-AC5F-644F6AE28AED}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4968,7 +5558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9F2A980-99F7-4378-B1A5-49E547FA6B9B}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5540,7 +6130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE5B189-3795-4D9F-8470-DCFD19DE4918}">
   <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6221,7 +6811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069A6CBD-9180-4207-8C39-A2C64C8EF28F}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6839,7 +7429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5E4505-E9C8-42A1-8718-1B515BF5CEF0}">
   <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7165,7 +7755,581 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58F52B2F-3150-4970-93DA-CF1EF1834400}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" customWidth="1"/>
+    <col min="7" max="7" width="27.7109375" customWidth="1"/>
+    <col min="14" max="14" width="5.42578125" customWidth="1"/>
+    <col min="15" max="15" width="6.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="8" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="12">
+        <v>13</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="H2" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="13">
+        <v>1</v>
+      </c>
+      <c r="J2" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K2" s="10">
+        <v>20</v>
+      </c>
+      <c r="L2" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="N2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="8">
+        <v>19</v>
+      </c>
+      <c r="P2" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I3" s="13">
+        <v>1</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K3" s="10">
+        <v>20</v>
+      </c>
+      <c r="L3" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M3" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="N3" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" s="8">
+        <v>19</v>
+      </c>
+      <c r="P3" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="13">
+        <v>1</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K4" s="10">
+        <v>20</v>
+      </c>
+      <c r="L4" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="8">
+        <v>19</v>
+      </c>
+      <c r="P4" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="13">
+        <v>1</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K5" s="10">
+        <v>20</v>
+      </c>
+      <c r="L5" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="8">
+        <v>19</v>
+      </c>
+      <c r="P5" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="13">
+        <v>1</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K6" s="10">
+        <v>20</v>
+      </c>
+      <c r="L6" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="N6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O6" s="8">
+        <v>19</v>
+      </c>
+      <c r="P6" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="H7" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="16">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K7" s="15">
+        <v>20</v>
+      </c>
+      <c r="L7" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="18">
+        <v>19</v>
+      </c>
+      <c r="P7" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K8" s="10">
+        <v>20</v>
+      </c>
+      <c r="L8" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="N8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="8">
+        <v>19</v>
+      </c>
+      <c r="P8" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="13">
+        <v>1</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K9" s="10">
+        <v>20</v>
+      </c>
+      <c r="L9" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="N9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O9" s="8">
+        <v>19</v>
+      </c>
+      <c r="P9" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="13">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K10" s="10">
+        <v>20</v>
+      </c>
+      <c r="L10" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O10" s="8">
+        <v>19</v>
+      </c>
+      <c r="P10" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="13">
+        <v>1</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="K11" s="10">
+        <v>20</v>
+      </c>
+      <c r="L11" s="13">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="N11" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="O11" s="8">
+        <v>19</v>
+      </c>
+      <c r="P11" s="10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="H12" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I12" s="16">
+        <v>1</v>
+      </c>
+      <c r="J12" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K12" s="15">
+        <v>20</v>
+      </c>
+      <c r="L12" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12" s="18">
+        <v>19</v>
+      </c>
+      <c r="P12" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="H13" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="16">
+        <v>1</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K13" s="15">
+        <v>20</v>
+      </c>
+      <c r="L13" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O13" s="18">
+        <v>19</v>
+      </c>
+      <c r="P13" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="I14" s="16">
+        <v>1</v>
+      </c>
+      <c r="J14" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K14" s="15">
+        <v>20</v>
+      </c>
+      <c r="L14" s="16">
+        <v>1000</v>
+      </c>
+      <c r="M14" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="O14" s="18">
+        <v>19</v>
+      </c>
+      <c r="P14" s="15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D20AA5E3-18D8-4B5E-AC08-AB63587E2B83}">
   <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7596,7 +8760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B95137-FEB9-4E2C-B66C-6707D12DE928}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8170,7 +9334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766A1B92-ECA3-413F-8793-59F03099027E}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8722,7 +9886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7D1D9CF-0A91-45D6-BABB-CA45EEB326F8}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9274,7 +10438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{465DD4B3-EF50-4C4C-8052-3ED0AB0386FC}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9782,7 +10946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D03594-4B69-4DBE-A832-A85A927E2ABB}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10334,7 +11498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DFD7390-D362-40FA-9656-E468CEDCF082}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10842,7 +12006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373A6E2E-7485-43B7-880B-A730001EE80C}">
   <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11348,578 +12512,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C757B42-67CE-4B78-B430-7A91DEAA5F92}">
-  <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4">
-        <v>13</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H3" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I3" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J3" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3">
-        <v>19</v>
-      </c>
-      <c r="P3" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I4" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K4" s="1">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4">
-        <v>19</v>
-      </c>
-      <c r="P4" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15</v>
-      </c>
-      <c r="L5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O5">
-        <v>19</v>
-      </c>
-      <c r="P5" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J6" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K6" s="1">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6">
-        <v>19</v>
-      </c>
-      <c r="P6" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I7" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J7" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K7" s="1">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7">
-        <v>19</v>
-      </c>
-      <c r="P7" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="H8" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J8" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K8" s="1">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>19</v>
-      </c>
-      <c r="P8" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K9" s="1">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O9">
-        <v>19</v>
-      </c>
-      <c r="P9" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J10" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K10" s="1">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K11" s="1">
-        <v>15</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O11">
-        <v>19</v>
-      </c>
-      <c r="P11" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" t="s">
-        <v>209</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K12" s="1">
-        <v>15</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12">
-        <v>19</v>
-      </c>
-      <c r="P12" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" t="s">
-        <v>210</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K13" s="1">
-        <v>15</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O13">
-        <v>19</v>
-      </c>
-      <c r="P13" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" t="s">
-        <v>211</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1E-4</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1E-3</v>
-      </c>
-      <c r="J14" s="2">
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K14" s="1">
-        <v>15</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="O14">
-        <v>19</v>
-      </c>
-      <c r="P14" s="1" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>